--- a/artfynd/A 6125-2026 artfynd.xlsx
+++ b/artfynd/A 6125-2026 artfynd.xlsx
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133248880</v>
+        <v>133275769</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>58119</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,45 +1120,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ryggmyran, Ryggmyran, Nb</t>
+          <t>Bräntberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787264</v>
+        <v>787376</v>
       </c>
       <c r="R6" t="n">
-        <v>7248291</v>
+        <v>7248193</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133275769</v>
+        <v>133248880</v>
       </c>
       <c r="B7" t="n">
-        <v>58119</v>
+        <v>57958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,49 +1229,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bräntberget, Nb</t>
+          <t>Ryggmyran, Ryggmyran, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>787376</v>
+        <v>787264</v>
       </c>
       <c r="R7" t="n">
-        <v>7248193</v>
+        <v>7248291</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 6125-2026 artfynd.xlsx
+++ b/artfynd/A 6125-2026 artfynd.xlsx
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133275769</v>
+        <v>133248880</v>
       </c>
       <c r="B6" t="n">
-        <v>58119</v>
+        <v>57958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,49 +1120,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bräntberget, Nb</t>
+          <t>Ryggmyran, Ryggmyran, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787376</v>
+        <v>787264</v>
       </c>
       <c r="R6" t="n">
-        <v>7248193</v>
+        <v>7248291</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133248880</v>
+        <v>133275769</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>58119</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,45 +1225,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ryggmyran, Ryggmyran, Nb</t>
+          <t>Bräntberget, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>787264</v>
+        <v>787376</v>
       </c>
       <c r="R7" t="n">
-        <v>7248291</v>
+        <v>7248193</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 6125-2026 artfynd.xlsx
+++ b/artfynd/A 6125-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1430,6 +1430,584 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133646362</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93206</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>787473</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7248546</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133646340</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99047</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>787281</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7248288</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133646215</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91938</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>787392</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7248395</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133646270</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83181</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>787352</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7248447</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133645907</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>787301</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7248501</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133646273</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83181</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>787276</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7248273</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6125-2026 artfynd.xlsx
+++ b/artfynd/A 6125-2026 artfynd.xlsx
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133275769</v>
+        <v>133248880</v>
       </c>
       <c r="B6" t="n">
-        <v>58119</v>
+        <v>57958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,49 +1120,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bräntberget, Nb</t>
+          <t>Ryggmyran, Ryggmyran, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787376</v>
+        <v>787264</v>
       </c>
       <c r="R6" t="n">
-        <v>7248193</v>
+        <v>7248291</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133248880</v>
+        <v>133275769</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>58119</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,45 +1225,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ryggmyran, Ryggmyran, Nb</t>
+          <t>Bräntberget, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>787264</v>
+        <v>787376</v>
       </c>
       <c r="R7" t="n">
-        <v>7248291</v>
+        <v>7248193</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>133646362</v>
       </c>
       <c r="B9" t="n">
-        <v>93206</v>
+        <v>93208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,34 +1529,30 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133646340</v>
+        <v>133646215</v>
       </c>
       <c r="B10" t="n">
-        <v>99047</v>
+        <v>91940</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1564,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>787281</v>
+        <v>787392</v>
       </c>
       <c r="R10" t="n">
-        <v>7248288</v>
+        <v>7248395</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,30 +1622,34 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133646215</v>
+        <v>133646340</v>
       </c>
       <c r="B11" t="n">
-        <v>91938</v>
+        <v>99049</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>787392</v>
+        <v>787281</v>
       </c>
       <c r="R11" t="n">
-        <v>7248395</v>
+        <v>7248288</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,7 +1722,7 @@
         <v>133646270</v>
       </c>
       <c r="B12" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>133646273</v>
       </c>
       <c r="B14" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6125-2026 artfynd.xlsx
+++ b/artfynd/A 6125-2026 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>133646362</v>
       </c>
       <c r="B9" t="n">
-        <v>93208</v>
+        <v>93216</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>133646215</v>
       </c>
       <c r="B10" t="n">
-        <v>91940</v>
+        <v>91948</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>133646340</v>
       </c>
       <c r="B11" t="n">
-        <v>99049</v>
+        <v>99057</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>133646270</v>
       </c>
       <c r="B12" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>133646273</v>
       </c>
       <c r="B14" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6125-2026 artfynd.xlsx
+++ b/artfynd/A 6125-2026 artfynd.xlsx
@@ -1529,30 +1529,34 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133646215</v>
+        <v>133646340</v>
       </c>
       <c r="B10" t="n">
-        <v>91980</v>
+        <v>99098</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1560,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>787392</v>
+        <v>787281</v>
       </c>
       <c r="R10" t="n">
-        <v>7248395</v>
+        <v>7248288</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,34 +1626,30 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133646340</v>
+        <v>133646215</v>
       </c>
       <c r="B11" t="n">
-        <v>99098</v>
+        <v>91980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>787281</v>
+        <v>787392</v>
       </c>
       <c r="R11" t="n">
-        <v>7248288</v>
+        <v>7248395</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 6125-2026 artfynd.xlsx
+++ b/artfynd/A 6125-2026 artfynd.xlsx
@@ -1435,7 +1435,7 @@
         <v>133646362</v>
       </c>
       <c r="B9" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,34 +1529,30 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133646340</v>
+        <v>133646215</v>
       </c>
       <c r="B10" t="n">
-        <v>99098</v>
+        <v>91987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1564,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>787281</v>
+        <v>787392</v>
       </c>
       <c r="R10" t="n">
-        <v>7248288</v>
+        <v>7248395</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,30 +1622,34 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133646215</v>
+        <v>133646340</v>
       </c>
       <c r="B11" t="n">
-        <v>91980</v>
+        <v>99105</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>787392</v>
+        <v>787281</v>
       </c>
       <c r="R11" t="n">
-        <v>7248395</v>
+        <v>7248288</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,7 +1722,7 @@
         <v>133646270</v>
       </c>
       <c r="B12" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>133646273</v>
       </c>
       <c r="B14" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6125-2026 artfynd.xlsx
+++ b/artfynd/A 6125-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130082220</v>
+        <v>133646270</v>
       </c>
       <c r="B2" t="n">
-        <v>57053</v>
+        <v>83222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>787464</v>
+        <v>787352</v>
       </c>
       <c r="R2" t="n">
-        <v>7248594</v>
+        <v>7248447</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,7 +757,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -792,57 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133248585</v>
+        <v>133646273</v>
       </c>
       <c r="B3" t="n">
-        <v>58349</v>
+        <v>83222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ryggmyran, Ryggmyran, Nb</t>
+          <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>787371</v>
+        <v>787276</v>
       </c>
       <c r="R3" t="n">
-        <v>7248343</v>
+        <v>7248273</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133247985</v>
+        <v>133646355</v>
       </c>
       <c r="B4" t="n">
-        <v>58410</v>
+        <v>93271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,46 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ryggmyran, Ryggmyran, Nb</t>
+          <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>787252</v>
+        <v>787515</v>
       </c>
       <c r="R4" t="n">
-        <v>7248519</v>
+        <v>7248394</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133248244</v>
+        <v>133646359</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>93271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,45 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ryggmyran, Ryggmyran, Nb</t>
+          <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>787421</v>
+        <v>787473</v>
       </c>
       <c r="R5" t="n">
-        <v>7248408</v>
+        <v>7248546</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,72 +1051,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133275769</v>
+        <v>133645907</v>
       </c>
       <c r="B6" t="n">
-        <v>58136</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bräntberget, Nb</t>
+          <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787376</v>
+        <v>787301</v>
       </c>
       <c r="R6" t="n">
-        <v>7248193</v>
+        <v>7248501</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,19 +1148,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133248880</v>
+        <v>133248244</v>
       </c>
       <c r="B7" t="n">
         <v>57975</v>
@@ -1251,7 +1193,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1261,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>787264</v>
+        <v>787421</v>
       </c>
       <c r="R7" t="n">
-        <v>7248291</v>
+        <v>7248408</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1323,27 +1265,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133420884</v>
+        <v>133248880</v>
       </c>
       <c r="B8" t="n">
-        <v>58349</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1351,32 +1293,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bräntberget, Nb</t>
+          <t>Ryggmyran, Ryggmyran, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>787366</v>
+        <v>787264</v>
       </c>
       <c r="R8" t="n">
-        <v>7248422</v>
+        <v>7248291</v>
       </c>
       <c r="S8" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133646362</v>
+        <v>130082220</v>
       </c>
       <c r="B9" t="n">
-        <v>93264</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,34 +1381,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>787473</v>
+        <v>787464</v>
       </c>
       <c r="R9" t="n">
-        <v>7248546</v>
+        <v>7248594</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,12 +1444,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,6 +1471,7 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1529,41 +1487,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133646215</v>
+        <v>130082222</v>
       </c>
       <c r="B10" t="n">
-        <v>91987</v>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>787392</v>
+        <v>787544</v>
       </c>
       <c r="R10" t="n">
-        <v>7248395</v>
+        <v>7248514</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,12 +1561,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,6 +1588,7 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AR10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1622,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133646340</v>
+        <v>130082221</v>
       </c>
       <c r="B11" t="n">
-        <v>99105</v>
+        <v>57144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,34 +1615,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>102613</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äggskal</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>787281</v>
+        <v>787533</v>
       </c>
       <c r="R11" t="n">
-        <v>7248288</v>
+        <v>7248521</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,12 +1678,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1704,6 +1705,7 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AR11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1719,10 +1721,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133646270</v>
+        <v>133247985</v>
       </c>
       <c r="B12" t="n">
-        <v>83215</v>
+        <v>58410</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,37 +1732,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>103001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Ryggmyran, Ryggmyran, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>787352</v>
+        <v>787252</v>
       </c>
       <c r="R12" t="n">
-        <v>7248447</v>
+        <v>7248519</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1784,12 +1795,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1804,39 +1815,39 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133645907</v>
+        <v>130081469</v>
       </c>
       <c r="B13" t="n">
-        <v>57972</v>
+        <v>58327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1844,17 +1855,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>787301</v>
+        <v>787222</v>
       </c>
       <c r="R13" t="n">
-        <v>7248501</v>
+        <v>7248516</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1881,12 +1901,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>05:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>05:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1898,6 +1928,7 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AR13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
@@ -1913,48 +1944,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133646273</v>
+        <v>133248585</v>
       </c>
       <c r="B14" t="n">
-        <v>83215</v>
+        <v>58349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Ryggmyran, Ryggmyran, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>787276</v>
+        <v>787371</v>
       </c>
       <c r="R14" t="n">
-        <v>7248273</v>
+        <v>7248343</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1978,12 +2018,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1998,15 +2038,439 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133420884</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bräntberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>787366</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7248422</v>
+      </c>
+      <c r="S15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133275769</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bräntberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>787376</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7248193</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133421003</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bräntberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>787272</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7248095</v>
+      </c>
+      <c r="S17" t="n">
+        <v>100</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133646340</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>787281</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7248288</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Elin Lindmark</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Via Elin Lindmark</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6125-2026 artfynd.xlsx
+++ b/artfynd/A 6125-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1370,57 +1370,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130082220</v>
+        <v>134158276</v>
       </c>
       <c r="B9" t="n">
-        <v>57141</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Ryggmyran, Ryggmyran, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>787464</v>
+        <v>787360</v>
       </c>
       <c r="R9" t="n">
-        <v>7248594</v>
+        <v>7248411</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1444,22 +1443,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,73 +1460,71 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AR9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130082222</v>
+        <v>134158502</v>
       </c>
       <c r="B10" t="n">
-        <v>57141</v>
+        <v>57975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Bräntberget, Bräntberget, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>787544</v>
+        <v>787266</v>
       </c>
       <c r="R10" t="n">
-        <v>7248514</v>
+        <v>7248287</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1561,22 +1548,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1588,26 +1565,25 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AR10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130082221</v>
+        <v>130082220</v>
       </c>
       <c r="B11" t="n">
-        <v>57144</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1615,21 +1591,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1639,7 +1615,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äggskal</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1648,10 +1624,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>787533</v>
+        <v>787464</v>
       </c>
       <c r="R11" t="n">
-        <v>7248521</v>
+        <v>7248594</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,7 +1659,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1693,7 +1669,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,32 +1697,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133247985</v>
+        <v>130082222</v>
       </c>
       <c r="B12" t="n">
-        <v>58410</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103001</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1756,22 +1732,22 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ryggmyran, Ryggmyran, Nb</t>
+          <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>787252</v>
+        <v>787544</v>
       </c>
       <c r="R12" t="n">
-        <v>7248519</v>
+        <v>7248514</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1795,12 +1771,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,25 +1798,26 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AR12" t="inlineStr"/>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130081469</v>
+        <v>130082221</v>
       </c>
       <c r="B13" t="n">
-        <v>58327</v>
+        <v>57144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,16 +1825,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>102613</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1862,7 +1849,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äggskal</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1871,10 +1858,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>787222</v>
+        <v>787533</v>
       </c>
       <c r="R13" t="n">
-        <v>7248516</v>
+        <v>7248521</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,22 +1888,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>05:14</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>05:14</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,32 +1931,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133248585</v>
+        <v>133247985</v>
       </c>
       <c r="B14" t="n">
-        <v>58349</v>
+        <v>58410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1979,7 +1966,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1988,13 +1975,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>787371</v>
+        <v>787252</v>
       </c>
       <c r="R14" t="n">
-        <v>7248343</v>
+        <v>7248519</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2050,10 +2037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133420884</v>
+        <v>130081469</v>
       </c>
       <c r="B15" t="n">
-        <v>58349</v>
+        <v>58327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2083,27 +2070,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bräntberget, Nb</t>
+          <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>787366</v>
+        <v>787222</v>
       </c>
       <c r="R15" t="n">
-        <v>7248422</v>
+        <v>7248516</v>
       </c>
       <c r="S15" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2127,12 +2111,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>05:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>05:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2144,47 +2138,48 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AR15" t="inlineStr"/>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133275769</v>
+        <v>133248585</v>
       </c>
       <c r="B16" t="n">
-        <v>58136</v>
+        <v>58349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2192,24 +2187,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bräntberget, Nb</t>
+          <t>Ryggmyran, Ryggmyran, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>787376</v>
+        <v>787371</v>
       </c>
       <c r="R16" t="n">
-        <v>7248193</v>
+        <v>7248343</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2268,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133421003</v>
+        <v>133420884</v>
       </c>
       <c r="B17" t="n">
-        <v>58596</v>
+        <v>58349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103041</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2315,13 +2307,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>787272</v>
+        <v>787366</v>
       </c>
       <c r="R17" t="n">
-        <v>7248095</v>
+        <v>7248422</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2377,48 +2369,60 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133646340</v>
+        <v>133275769</v>
       </c>
       <c r="B18" t="n">
-        <v>99112</v>
+        <v>58136</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Bräntberget, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>787281</v>
+        <v>787376</v>
       </c>
       <c r="R18" t="n">
-        <v>7248288</v>
+        <v>7248193</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2442,12 +2446,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2462,15 +2466,221 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133421003</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bräntberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>787272</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7248095</v>
+      </c>
+      <c r="S19" t="n">
+        <v>100</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133646340</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>787281</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7248288</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Elin Lindmark</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Via Elin Lindmark</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6125-2026 artfynd.xlsx
+++ b/artfynd/A 6125-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133646270</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133646273</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133646355</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133646359</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133645907</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133248244</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133248880</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134158276</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134158502</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1694,6 +1744,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130082220</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1811,6 +1866,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130082222</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1928,6 +1988,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130082221</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2034,6 +2099,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133247985</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2151,6 +2221,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130081469</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2257,6 +2332,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133248585</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2366,6 +2446,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133420884</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2475,6 +2560,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275769</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2584,6 +2674,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133421003</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2681,8 +2776,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133646340</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>